--- a/diseases/d115/2005-2009.xlsx
+++ b/diseases/d115/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1309,9 +1306,6 @@
       <c r="O5" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.3368880638874524</v>
       </c>
@@ -1705,9 +1699,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -2001,9 +1992,6 @@
       <c r="O9" t="n">
         <v>3</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.05718553388986295</v>
       </c>
@@ -2397,9 +2385,6 @@
       <c r="O11" t="n">
         <v>1</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.00208979235906712</v>
       </c>
@@ -2693,9 +2678,6 @@
       <c r="O13" t="n">
         <v>1</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -3089,9 +3071,6 @@
       <c r="O15" t="n">
         <v>2</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.004179584718134241</v>
       </c>
@@ -3385,9 +3364,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3781,9 +3757,6 @@
       <c r="O19" t="n">
         <v>1</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0.00208979235906712</v>
       </c>
@@ -4077,9 +4050,6 @@
       <c r="O21" t="n">
         <v>5</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.09530922314977158</v>
       </c>
@@ -4473,9 +4443,6 @@
       <c r="O23" t="n">
         <v>2</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.004179584718134241</v>
       </c>
@@ -4769,9 +4736,6 @@
       <c r="O25" t="n">
         <v>5</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.09530922314977158</v>
       </c>
@@ -5165,9 +5129,6 @@
       <c r="O27" t="n">
         <v>9</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.01880813123160408</v>
       </c>
@@ -5461,9 +5422,6 @@
       <c r="O29" t="n">
         <v>1</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -5857,9 +5815,6 @@
       <c r="O31" t="n">
         <v>11</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.02298771594973832</v>
       </c>
@@ -6153,9 +6108,6 @@
       <c r="O33" t="n">
         <v>3</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.05718553388986295</v>
       </c>
@@ -6549,9 +6501,6 @@
       <c r="O35" t="n">
         <v>6</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.01253875415440272</v>
       </c>
@@ -6845,9 +6794,6 @@
       <c r="O37" t="n">
         <v>1</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -7241,9 +7187,6 @@
       <c r="O39" t="n">
         <v>4</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.008359169436268481</v>
       </c>
@@ -7537,9 +7480,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -7933,9 +7873,6 @@
       <c r="O43" t="n">
         <v>4</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.008359169436268481</v>
       </c>
@@ -8229,9 +8166,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -8625,9 +8559,6 @@
       <c r="O47" t="n">
         <v>3</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.00626937707720136</v>
       </c>
@@ -8921,9 +8852,6 @@
       <c r="O49" t="n">
         <v>4</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.07624737851981726</v>
       </c>
@@ -9317,9 +9245,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -9613,9 +9538,6 @@
       <c r="O53" t="n">
         <v>2</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.03797771334858708</v>
       </c>
@@ -10009,9 +9931,6 @@
       <c r="O55" t="n">
         <v>1</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.3290837649815384</v>
       </c>
@@ -10405,9 +10324,6 @@
       <c r="O57" t="n">
         <v>2</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.004166100988266854</v>
       </c>
@@ -11293,9 +11209,6 @@
       <c r="O63" t="n">
         <v>1</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -11689,9 +11602,6 @@
       <c r="O65" t="n">
         <v>1</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.002083050494133427</v>
       </c>
@@ -12577,9 +12487,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -12973,9 +12880,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -13861,9 +13765,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -14257,9 +14158,6 @@
       <c r="O81" t="n">
         <v>2</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.004166100988266854</v>
       </c>
@@ -15293,9 +15191,6 @@
       <c r="O88" t="n">
         <v>1</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -15689,9 +15584,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -16577,9 +16469,6 @@
       <c r="O96" t="n">
         <v>1</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -16973,9 +16862,6 @@
       <c r="O98" t="n">
         <v>10</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.02083050494133427</v>
       </c>
@@ -17861,9 +17747,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -18257,9 +18140,6 @@
       <c r="O106" t="n">
         <v>7</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.01458135345893399</v>
       </c>
@@ -19293,9 +19173,6 @@
       <c r="O113" t="n">
         <v>1</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -19689,9 +19566,6 @@
       <c r="O115" t="n">
         <v>5</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.01041525247066713</v>
       </c>
@@ -20577,9 +20451,6 @@
       <c r="O121" t="n">
         <v>1</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -20973,9 +20844,6 @@
       <c r="O123" t="n">
         <v>5</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.01041525247066713</v>
       </c>
@@ -22009,9 +21877,6 @@
       <c r="O130" t="n">
         <v>2</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.03797771334858708</v>
       </c>
@@ -22405,9 +22270,6 @@
       <c r="O132" t="n">
         <v>1</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.002083050494133427</v>
       </c>
@@ -23293,9 +23155,6 @@
       <c r="O138" t="n">
         <v>4</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.07595542669717416</v>
       </c>
@@ -23689,9 +23548,6 @@
       <c r="O140" t="n">
         <v>4</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.008332201976533707</v>
       </c>
@@ -24577,9 +24433,6 @@
       <c r="O146" t="n">
         <v>1</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -24973,9 +24826,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -26009,9 +25859,6 @@
       <c r="O155" t="n">
         <v>2</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.03781640513471149</v>
       </c>
@@ -26405,9 +26252,6 @@
       <c r="O157" t="n">
         <v>13</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>4.171339368940528</v>
       </c>
@@ -26801,9 +26645,6 @@
       <c r="O159" t="n">
         <v>1</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.002075631077207799</v>
       </c>
@@ -27689,9 +27530,6 @@
       <c r="O165" t="n">
         <v>2</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.03781640513471149</v>
       </c>
@@ -28085,9 +27923,6 @@
       <c r="O167" t="n">
         <v>1</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0.002075631077207799</v>
       </c>
@@ -28973,9 +28808,6 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
@@ -29369,9 +29201,6 @@
       <c r="O175" t="n">
         <v>1</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.002075631077207799</v>
       </c>
@@ -30405,9 +30234,6 @@
       <c r="O182" t="n">
         <v>0</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0</v>
       </c>
@@ -30801,9 +30627,6 @@
       <c r="O184" t="n">
         <v>1</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0.002075631077207799</v>
       </c>
@@ -31689,9 +31512,6 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
@@ -32085,9 +31905,6 @@
       <c r="O192" t="n">
         <v>6</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.01245378646324679</v>
       </c>
@@ -32973,9 +32790,6 @@
       <c r="O198" t="n">
         <v>1</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -33369,9 +33183,6 @@
       <c r="O200" t="n">
         <v>4</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.008302524308831197</v>
       </c>
@@ -34405,9 +34216,6 @@
       <c r="O207" t="n">
         <v>1</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -34801,9 +34609,6 @@
       <c r="O209" t="n">
         <v>9</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>0.01868067969487019</v>
       </c>
@@ -35689,9 +35494,6 @@
       <c r="O215" t="n">
         <v>1</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -36085,9 +35887,6 @@
       <c r="O217" t="n">
         <v>11</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0.02283194184928579</v>
       </c>
@@ -36973,9 +36772,6 @@
       <c r="O223" t="n">
         <v>1</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -37369,9 +37165,6 @@
       <c r="O225" t="n">
         <v>2</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0.004151262154415599</v>
       </c>
@@ -38405,9 +38198,6 @@
       <c r="O232" t="n">
         <v>2</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0.03781640513471149</v>
       </c>
@@ -38801,9 +38591,6 @@
       <c r="O234" t="n">
         <v>4</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0.008302524308831197</v>
       </c>
@@ -39689,9 +39476,6 @@
       <c r="O240" t="n">
         <v>2</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0.03781640513471149</v>
       </c>
@@ -40085,9 +39869,6 @@
       <c r="O242" t="n">
         <v>0</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>0</v>
       </c>
@@ -40973,9 +40754,6 @@
       <c r="O248" t="n">
         <v>0</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0</v>
       </c>
@@ -41369,9 +41147,6 @@
       <c r="O250" t="n">
         <v>1</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0.002075631077207799</v>
       </c>
@@ -42405,9 +42180,6 @@
       <c r="O257" t="n">
         <v>0</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="R257" t="n">
         <v>0</v>
       </c>
@@ -42801,9 +42573,6 @@
       <c r="O259" t="n">
         <v>4</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>1.259784986197481</v>
       </c>
@@ -43197,9 +42966,6 @@
       <c r="O261" t="n">
         <v>3</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="R261" t="n">
         <v>0.006203923845345857</v>
       </c>
@@ -44085,9 +43851,6 @@
       <c r="O267" t="n">
         <v>0</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0</v>
       </c>
@@ -44481,9 +44244,6 @@
       <c r="O269" t="n">
         <v>1</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0.002067974615115286</v>
       </c>
@@ -45369,9 +45129,6 @@
       <c r="O275" t="n">
         <v>1</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -45765,9 +45522,6 @@
       <c r="O277" t="n">
         <v>2</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>0.004135949230230571</v>
       </c>
@@ -46801,9 +46555,6 @@
       <c r="O284" t="n">
         <v>0</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>0</v>
       </c>
@@ -47197,9 +46948,6 @@
       <c r="O286" t="n">
         <v>2</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>0.004135949230230571</v>
       </c>
@@ -48085,9 +47833,6 @@
       <c r="O292" t="n">
         <v>1</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -48481,9 +48226,6 @@
       <c r="O294" t="n">
         <v>4</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>0.008271898460461143</v>
       </c>
@@ -49517,9 +49259,6 @@
       <c r="O301" t="n">
         <v>0</v>
       </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
       <c r="R301" t="n">
         <v>0</v>
       </c>
@@ -49913,9 +49652,6 @@
       <c r="O303" t="n">
         <v>7</v>
       </c>
-      <c r="Q303" t="n">
-        <v>0</v>
-      </c>
       <c r="R303" t="n">
         <v>0.014475822305807</v>
       </c>
@@ -50801,9 +50537,6 @@
       <c r="O309" t="n">
         <v>3</v>
       </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
       <c r="R309" t="n">
         <v>0.05646126747640907</v>
       </c>
@@ -51345,9 +51078,6 @@
       <c r="O312" t="n">
         <v>8</v>
       </c>
-      <c r="Q312" t="n">
-        <v>0</v>
-      </c>
       <c r="R312" t="n">
         <v>0.01654379692092229</v>
       </c>
@@ -52233,9 +51963,6 @@
       <c r="O318" t="n">
         <v>0</v>
       </c>
-      <c r="Q318" t="n">
-        <v>0</v>
-      </c>
       <c r="R318" t="n">
         <v>0</v>
       </c>
@@ -52777,9 +52504,6 @@
       <c r="O321" t="n">
         <v>9</v>
       </c>
-      <c r="Q321" t="n">
-        <v>0</v>
-      </c>
       <c r="R321" t="n">
         <v>0.01861177153603757</v>
       </c>
@@ -53813,9 +53537,6 @@
       <c r="O328" t="n">
         <v>2</v>
       </c>
-      <c r="Q328" t="n">
-        <v>0</v>
-      </c>
       <c r="R328" t="n">
         <v>0.03764084498427271</v>
       </c>
@@ -54357,9 +54078,6 @@
       <c r="O331" t="n">
         <v>3</v>
       </c>
-      <c r="Q331" t="n">
-        <v>0</v>
-      </c>
       <c r="R331" t="n">
         <v>0.006203923845345857</v>
       </c>
@@ -55245,9 +54963,6 @@
       <c r="O337" t="n">
         <v>1</v>
       </c>
-      <c r="Q337" t="n">
-        <v>0</v>
-      </c>
       <c r="R337" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -55789,9 +55504,6 @@
       <c r="O340" t="n">
         <v>6</v>
       </c>
-      <c r="Q340" t="n">
-        <v>0</v>
-      </c>
       <c r="R340" t="n">
         <v>0.01240784769069171</v>
       </c>
@@ -56677,9 +56389,6 @@
       <c r="O346" t="n">
         <v>0</v>
       </c>
-      <c r="Q346" t="n">
-        <v>0</v>
-      </c>
       <c r="R346" t="n">
         <v>0</v>
       </c>
@@ -57221,9 +56930,6 @@
       <c r="O349" t="n">
         <v>7</v>
       </c>
-      <c r="Q349" t="n">
-        <v>0</v>
-      </c>
       <c r="R349" t="n">
         <v>0.014475822305807</v>
       </c>
@@ -58257,9 +57963,6 @@
       <c r="O356" t="n">
         <v>0</v>
       </c>
-      <c r="Q356" t="n">
-        <v>0</v>
-      </c>
       <c r="R356" t="n">
         <v>0</v>
       </c>
@@ -58801,9 +58504,6 @@
       <c r="O359" t="n">
         <v>6</v>
       </c>
-      <c r="Q359" t="n">
-        <v>0</v>
-      </c>
       <c r="R359" t="n">
         <v>0.01240784769069171</v>
       </c>
@@ -59689,9 +59389,6 @@
       <c r="O365" t="n">
         <v>1</v>
       </c>
-      <c r="Q365" t="n">
-        <v>0</v>
-      </c>
       <c r="R365" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -60233,9 +59930,6 @@
       <c r="O368" t="n">
         <v>9</v>
       </c>
-      <c r="Q368" t="n">
-        <v>0</v>
-      </c>
       <c r="R368" t="n">
         <v>2.824752363376144</v>
       </c>
@@ -60629,9 +60323,6 @@
       <c r="O370" t="n">
         <v>0</v>
       </c>
-      <c r="Q370" t="n">
-        <v>0</v>
-      </c>
       <c r="R370" t="n">
         <v>0</v>
       </c>
@@ -61665,9 +61356,6 @@
       <c r="O377" t="n">
         <v>0</v>
       </c>
-      <c r="Q377" t="n">
-        <v>0</v>
-      </c>
       <c r="R377" t="n">
         <v>0</v>
       </c>
@@ -62209,9 +61897,6 @@
       <c r="O380" t="n">
         <v>0</v>
       </c>
-      <c r="Q380" t="n">
-        <v>0</v>
-      </c>
       <c r="R380" t="n">
         <v>0</v>
       </c>
@@ -63097,9 +62782,6 @@
       <c r="O386" t="n">
         <v>0</v>
       </c>
-      <c r="Q386" t="n">
-        <v>0</v>
-      </c>
       <c r="R386" t="n">
         <v>0</v>
       </c>
@@ -63641,9 +63323,6 @@
       <c r="O389" t="n">
         <v>3</v>
       </c>
-      <c r="Q389" t="n">
-        <v>0</v>
-      </c>
       <c r="R389" t="n">
         <v>0.00617961845861509</v>
       </c>
@@ -64529,9 +64208,6 @@
       <c r="O395" t="n">
         <v>0</v>
       </c>
-      <c r="Q395" t="n">
-        <v>0</v>
-      </c>
       <c r="R395" t="n">
         <v>0</v>
       </c>
@@ -65073,9 +64749,6 @@
       <c r="O398" t="n">
         <v>4</v>
       </c>
-      <c r="Q398" t="n">
-        <v>0</v>
-      </c>
       <c r="R398" t="n">
         <v>0.008239491278153453</v>
       </c>
@@ -65961,9 +65634,6 @@
       <c r="O404" t="n">
         <v>4</v>
       </c>
-      <c r="Q404" t="n">
-        <v>0</v>
-      </c>
       <c r="R404" t="n">
         <v>0.07492241081962027</v>
       </c>
@@ -66505,9 +66175,6 @@
       <c r="O407" t="n">
         <v>7</v>
       </c>
-      <c r="Q407" t="n">
-        <v>0</v>
-      </c>
       <c r="R407" t="n">
         <v>0.01441910973676854</v>
       </c>
@@ -67541,9 +67208,6 @@
       <c r="O414" t="n">
         <v>1</v>
       </c>
-      <c r="Q414" t="n">
-        <v>0</v>
-      </c>
       <c r="R414" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -68085,9 +67749,6 @@
       <c r="O417" t="n">
         <v>21</v>
       </c>
-      <c r="Q417" t="n">
-        <v>0</v>
-      </c>
       <c r="R417" t="n">
         <v>0.04325732921030563</v>
       </c>
@@ -68973,9 +68634,6 @@
       <c r="O423" t="n">
         <v>10</v>
       </c>
-      <c r="Q423" t="n">
-        <v>0</v>
-      </c>
       <c r="R423" t="n">
         <v>0.1873060270490507</v>
       </c>
@@ -69517,9 +69175,6 @@
       <c r="O426" t="n">
         <v>11</v>
       </c>
-      <c r="Q426" t="n">
-        <v>0</v>
-      </c>
       <c r="R426" t="n">
         <v>0.022658601014922</v>
       </c>
@@ -70405,9 +70060,6 @@
       <c r="O432" t="n">
         <v>7</v>
       </c>
-      <c r="Q432" t="n">
-        <v>0</v>
-      </c>
       <c r="R432" t="n">
         <v>0.1311142189343355</v>
       </c>
@@ -70949,9 +70601,6 @@
       <c r="O435" t="n">
         <v>4</v>
       </c>
-      <c r="Q435" t="n">
-        <v>0</v>
-      </c>
       <c r="R435" t="n">
         <v>0.008239491278153453</v>
       </c>
@@ -71985,9 +71634,6 @@
       <c r="O442" t="n">
         <v>1</v>
       </c>
-      <c r="Q442" t="n">
-        <v>0</v>
-      </c>
       <c r="R442" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -72529,9 +72175,6 @@
       <c r="O445" t="n">
         <v>4</v>
       </c>
-      <c r="Q445" t="n">
-        <v>0</v>
-      </c>
       <c r="R445" t="n">
         <v>0.008239491278153453</v>
       </c>
@@ -73417,9 +73060,6 @@
       <c r="O451" t="n">
         <v>5</v>
       </c>
-      <c r="Q451" t="n">
-        <v>0</v>
-      </c>
       <c r="R451" t="n">
         <v>0.09365301352452535</v>
       </c>
@@ -73961,9 +73601,6 @@
       <c r="O454" t="n">
         <v>4</v>
       </c>
-      <c r="Q454" t="n">
-        <v>0</v>
-      </c>
       <c r="R454" t="n">
         <v>0.008239491278153453</v>
       </c>
@@ -74997,9 +74634,6 @@
       <c r="O461" t="n">
         <v>0</v>
       </c>
-      <c r="Q461" t="n">
-        <v>0</v>
-      </c>
       <c r="R461" t="n">
         <v>0</v>
       </c>
@@ -75541,9 +75175,6 @@
       <c r="O464" t="n">
         <v>2</v>
       </c>
-      <c r="Q464" t="n">
-        <v>0</v>
-      </c>
       <c r="R464" t="n">
         <v>0.004119745639076727</v>
       </c>
@@ -76429,9 +76060,6 @@
       <c r="O470" t="n">
         <v>0</v>
       </c>
-      <c r="Q470" t="n">
-        <v>0</v>
-      </c>
       <c r="R470" t="n">
         <v>0</v>
       </c>
@@ -76972,9 +76600,6 @@
       </c>
       <c r="O473" t="n">
         <v>2</v>
-      </c>
-      <c r="Q473" t="n">
-        <v>0</v>
       </c>
       <c r="R473" t="n">
         <v>0.004119745639076727</v>
